--- a/uploads/users.xlsx
+++ b/uploads/users.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>astha</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
